--- a/erp-server/erp-server-file/src/main/resources/excel/oms/InvoiceInvalid.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/InvoiceInvalid.xlsx
@@ -71,7 +71,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,19 +85,13 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Microsoft YaHei"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -579,137 +573,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -717,10 +711,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1061,19 +1052,19 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
